--- a/v6/files/r-customer-base.xlsx
+++ b/v6/files/r-customer-base.xlsx
@@ -876,7 +876,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Рассылать можно только тем, кто согласился получать сообщения.</t>
+          <t>Рекламу рассылать можно только тем, кто заранее согласился её получать (статья 18 закона «О рекламе»).</t>
         </is>
       </c>
     </row>

--- a/v6/files/r-customer-base.xlsx
+++ b/v6/files/r-customer-base.xlsx
@@ -855,7 +855,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Одна строка на заказ. Вместо имени, телефона и почты ставьте обезличенный номер клиента (например, К-001). Таблицу с контактами здесь не держите.</t>
+          <t>Одна строка на заказ. Вместо имени, телефона и почты ставьте обезличенный номер клиента (например, К-001). Таблицу с контактами здесь не держите. Контакты покупателей это персональные данные: по 152-ФЗ собирайте и храните их в базах на территории России, согласие на обработку с 1 сентября 2025 года берите отдельным документом, а до начала обработки подайте уведомление в Роскомнадзор.</t>
         </is>
       </c>
     </row>
